--- a/templates/입력3_연간근무표_2026-08.xlsx
+++ b/templates/입력3_연간근무표_2026-08.xlsx
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -571,103 +571,110 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>구성</t>
+          <t>※ 이 앱은 '전입'·'전입일' 열이 있는 이 양식만 받습니다. 그 열이 없는 예전 양식은 전입자를 표시할 방법이 없어 조용히 누락되므로 업로드 시 반려됩니다. 예전 파일을 갖고 계시면 이 양식을 새로 받으시거나, 이번 달 근무표를 만든 뒤 받은 '연간근무표'(출력②)를 쓰시면 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>· 인원 정보 — 순번·이름·직급·숙련도·가능근무·비고·전입·전입일. 파트장이 맨 위, 나머지는 입력①에 등록된 순서 그대로 나열됩니다.</t>
+          <t>구성</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>· 누적 통계 — 누적야간·누적근무일·누적오프·누적주말야간·누적2일블록·누적3일블록·반영개월수·최근야간점수(참고용)·누적D·누적E·누적prn·누적주말휴일오프·잔휴. 형평성(균등 배정)을 판단하는 데 참고로 쓰이며, 매달 생성할 때마다 자동 갱신됩니다.</t>
+          <t>· 인원 정보 — 순번·이름·직급·숙련도·가능근무·비고·전입·전입일. 파트장이 맨 위, 나머지는 입력①에 등록된 순서 그대로 나열됩니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>· 연간 근무 그리드 — 1월 1일부터 지금까지의 근무 이력. 화면에는 참고용으로만 보이지만, 이 중 가장 최근 한 달치는 전월이월값(연속근무일수·말일연속야간 등)을 자동으로 역산하는 데 실제로 쓰입니다.</t>
+          <t>· 누적 통계 — 누적야간·누적근무일·누적오프·누적주말야간·누적2일블록·누적3일블록·반영개월수·최근야간점수(참고용)·누적D·누적E·누적prn·누적주말휴일오프·잔휴. 형평성(균등 배정)을 판단하는 데 참고로 쓰이며, 매달 생성할 때마다 자동 갱신됩니다.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>전입자(다른 병동에서 오신 분)를 넣을 때</t>
+          <t>· 연간 근무 그리드 — 1월 1일부터 지금까지의 근무 이력. 화면에는 참고용으로만 보이지만, 이 중 가장 최근 한 달치는 전월이월값(연속근무일수·말일연속야간 등)을 자동으로 역산하는 데 실제로 쓰입니다.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>① 기존 인원 목록 바로 아래(맨 아래 '레벨평균' 줄보다 위)에 행을 추가하고 이름·직급·숙련도·가능근무를 적습니다. 이름은 입력②(원티드표)와 정확히 같아야 합니다.</t>
+          <t>전입자(다른 병동에서 오신 분)를 넣을 때</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>② '전입' 칸을 클릭해 드롭다운에서 '전입'을 고릅니다(직접 타이핑하지 않아도 됩니다).</t>
+          <t>① 기존 인원 목록 바로 아래(맨 아래 '레벨평균' 줄보다 위)에 행을 추가하고 이름·직급·숙련도·가능근무를 적습니다. 이름은 입력②(원티드표)와 정확히 같아야 합니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>③ 월중에 오신 분이면 '전입일' 칸에 날짜를 넣습니다. 비워두면 그 달 1일자 전입으로 봅니다.</t>
+          <t>② '전입' 칸을 클릭해 드롭다운에서 '전입'을 고릅니다(직접 타이핑하지 않아도 됩니다).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>④ 전 병동 근무기록을 받아오셨으면 날짜 칸에 날짜를 맞춰 붙여넣습니다(최소 직전 1개월, 3개월이면 야간 형평성까지 정확해집니다). 야간 후 휴식 규칙이 첫날부터 지켜지므로 가능하면 꼭 넣어주세요.</t>
+          <t>③ 월중에 오신 분이면 '전입일' 칸에 날짜를 넣습니다. 비워두면 그 달 1일자 전입으로 봅니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>⑤ '잔휴' 칸에 전 병동에서 넘겨받은 잔휴 숫자를 적습니다. 잔휴는 근무표만으로는 계산되지 않는 값이라 이것만은 직접 넣어주셔야 합니다(비우면 0으로 진행하고 안내가 뜹니다).</t>
+          <t>④ 전 병동 근무기록을 받아오셨으면 날짜 칸에 날짜를 맞춰 붙여넣습니다(최소 직전 1개월, 3개월이면 야간 형평성까지 정확해집니다). 야간 후 휴식 규칙이 첫날부터 지켜지므로 가능하면 꼭 넣어주세요.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>⑥ 누적야간·반영개월수 같은 누적 통계 칸은 비워두세요 — 부서 누적 실적은 우리 병동에 오신 시점부터 0에서 시작합니다.</t>
+          <t>⑤ '잔휴' 칸에 전 병동에서 넘겨받은 잔휴 숫자를 적습니다. 잔휴는 근무표만으로는 계산되지 않는 값이라 이것만은 직접 넣어주셔야 합니다(비우면 0으로 진행하고 안내가 뜹니다).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>전출자(이번 달 명단에서 빠진 분)</t>
+          <t>⑥ 누적야간·반영개월수 같은 누적 통계 칸은 비워두세요 — 부서 누적 실적은 우리 병동에 오신 시점부터 0에서 시작합니다.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>따로 적으실 게 없습니다. 입력②(이번 달 명단)에 없으면 자동으로 전출로 보고 이번 달 배정에서 빼며, 그동안 쌓인 이력은 아래쪽 '전출' 구분 행 밑에 그대로 보존됩니다.</t>
+          <t>전출자(이번 달 명단에서 빠진 분)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>처음 쓰는 병동이라면</t>
+          <t>따로 적으실 게 없습니다. 입력②(이번 달 명단)에 없으면 자동으로 전출로 보고 이번 달 배정에서 빼며, 그동안 쌓인 이력은 아래쪽 '전출' 구분 행 밑에 그대로 보존됩니다.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
+        <is>
+          <t>처음 쓰는 병동이라면</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>이 파일 없이 생략해도 됩니다 — 입력①②만으로 근무표 생성이 가능하고, 이 앱이 매달 자동으로 연간근무표를 만들어 드리니 다음 달부터 이어받으면 됩니다.</t>
         </is>
